--- a/docs/sample_report.xlsx
+++ b/docs/sample_report.xlsx
@@ -12,13 +12,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Machine" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues To Fix" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Entries (Clean)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dispatch Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Summary'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By Shift'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Machine'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Issues To Fix'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Issues To Fix'!$A$1:$I$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'All Entries (Clean)'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Stock Summary'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Dispatch Summary'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1013,16 +1017,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="61" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1033,30 +1039,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Machine</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Where To Fix</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -1068,30 +1084,36 @@
           <t>ERROR</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Rejected (820) is more than produced (780). Left out of totals</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>press_shop_15-10-2026.xlsx / Production row 7</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>rejected_gt_produced</t>
         </is>
@@ -1103,242 +1125,260 @@
           <t>ERROR</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Not a number: produced qty = 'approx 750' — left out of totals until corrected</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>press_shop_15-10-2026.xlsx / Production row 10</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>unreadable</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>46309</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>M02</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Produced 610 vs target 1000 (61%) (remark: Die change + power cut)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>press_shop_14-10-2026.xlsx / Production row 9</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>below_target</t>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>NUT-M8</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Issued 1,800 nos but only 1,500 was in stock — a receipt is missing or was entered late</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>stores_stock_register_oct-2026.xlsx / Stock Register row 13</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>stock_negative</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>M05</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Rejection 10.7% is above the 5% limit</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>cnc_2026-10-14.xlsx / Shift B row 3</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>high_rejection</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>BOX-50</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Not a number: issued qty = 'approx 30' — left out of the balance until corrected</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>stores_stock_register_oct-2026.xlsx / Stock Register row 20</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>stock_unreadable</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>46309</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>M05</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Produced 290 vs target 400 (72%) — no remark given</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>cnc_2026-10-14.xlsx / Shift B row 3</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>below_target</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>CRCA-12</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Balance written as 2,330, but 2,750 + 0 received − 520 issued = 2,230 (off by +100)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>stores_stock_register_oct-2026.xlsx / Stock Register row 7</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>stock_balance_mismatch</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>M01</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Revised figure used: produced 1190 replaces 11900 from press_shop_15-10-2026.xlsx</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>press_shop_15-10-2026_revised.xlsx / Production row 5</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>revised</t>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>PWD-BLK</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>GRN-1044 is entered twice (also stores_stock_register_oct-2026.xlsx row 16). If it's the same delivery, stock is overstated by 40 kg</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>stores_stock_register_oct-2026.xlsx / Stock Register row 17</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>stock_duplicate_ref</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>M02</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Produced 640 vs target 1000 (64%) — no remark given</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>press_shop_15-10-2026.xlsx / Production row 6</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>below_target</t>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>BSH-044</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Sent 1,100 against an order of 1,000 for CP-0091 / BSH-044 — 100 extra. A wrong entry, or does the customer know?</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>dispatch_register_oct-2026.xlsx / Dispatch Register row 13</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>dispatch_over</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>WARNING</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>M02</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>120 min downtime with no reason written</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>press_shop_15-10-2026.xlsx / Production row 9</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>downtime_no_reason</t>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>SFT-119</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Invoice INV-0414 is also used for CP-0091 / BSH-044 (dispatch_register_oct-2026.xlsx row 10). One invoice should be one truck for one order</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>dispatch_register_oct-2026.xlsx / Dispatch Register row 11</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>dispatch_duplicate_invoice</t>
         </is>
       </c>
     </row>
@@ -1348,247 +1388,720 @@
           <t>WARNING</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Produced 610 vs target 1000 (61%) (remark: Die change + power cut)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>press_shop_14-10-2026.xlsx / Production row 9</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>below_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>M05</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Rejection 10.7% is above the 5% limit</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>cnc_2026-10-14.xlsx / Shift B row 3</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>high_rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>M05</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Produced 290 vs target 400 (72%) — no remark given</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>cnc_2026-10-14.xlsx / Shift B row 3</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>below_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
         <v>46310</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Revised figure used: produced 1190 replaces 11900 from press_shop_15-10-2026.xlsx</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>press_shop_15-10-2026_revised.xlsx / Production row 5</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Produced 640 vs target 1000 (64%) — no remark given</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>press_shop_15-10-2026.xlsx / Production row 6</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>below_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>120 min downtime with no reason written</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>press_shop_15-10-2026.xlsx / Production row 9</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>downtime_no_reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>No entry for M05 in shift B — machine idle, or sheet not filled?</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>missing_entry</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>MSROD-8</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>MSROD-8 is at 50 kg, at or below its reorder level of 100. Raise a purchase order</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>stores_stock_register_oct-2026.xlsx / Stock Register row 11</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>stock_low</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>SFT-118</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>No POD for invoice INV-0388 after 10 days — the payment can't be chased</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>dispatch_register_oct-2026.xlsx / Dispatch Register row 4</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>dispatch_no_pod</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>BRK-221</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>REW/88 / BRK-221: 1,500 still to send, 4 days past the due date (11 Oct)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>dispatch_register_oct-2026.xlsx / Dispatch Register row 7</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>dispatch_overdue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Cross-check</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>BRK220</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>BRK220 is dispatched but isn't in the production sheets or the stock register. Did you mean BRK-220?</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>dispatch_register_oct-2026.xlsx / Dispatch Register row 14</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>cross_unknown_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Cross-check</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>HNG-310</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Dispatched 1,800 HNG-310 on 14–15 Oct, but the production sheets show only 1,584 good pieces made on those days. Was the rest from earlier stock? Add finished goods to the stock register to check properly</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>dispatch_register_oct-2026.xlsx / Dispatch Register row 12</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>cross_dispatch_gt_production</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
         <v>46309</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Exact copy of press_shop_14-10-2026.xlsx row 5 — counted once</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>press_shop_14-10-2026 (1).xlsx / Production row 5</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
         <v>46309</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Exact copy of press_shop_14-10-2026.xlsx row 6 — counted once</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>press_shop_14-10-2026 (1).xlsx / Production row 6</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
         <v>46309</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Exact copy of press_shop_14-10-2026.xlsx row 7 — counted once</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>press_shop_14-10-2026 (1).xlsx / Production row 7</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
         <v>46309</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Exact copy of press_shop_14-10-2026.xlsx row 8 — counted once</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>press_shop_14-10-2026 (1).xlsx / Production row 8</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
         <v>46309</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Exact copy of press_shop_14-10-2026.xlsx row 9 — counted once</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>press_shop_14-10-2026 (1).xlsx / Production row 9</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
         <v>46309</v>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Exact copy of press_shop_14-10-2026.xlsx row 10 — counted once</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>press_shop_14-10-2026 (1).xlsx / Production row 10</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:I27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2909,4 +3422,712 @@
   <autoFilter ref="A1:N24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Item Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Uom</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Closing</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Closing As Written</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Reorder Level</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CRCA-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CRCA sheet 1.2 mm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1930</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="I2" t="n">
+        <v>500</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MSROD-8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MS round rod 8 mm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUT-M8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hex nut M8</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nos</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4700</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4700</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PWD-BLK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Powder coat, black</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H5" t="n">
+        <v>110</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BOX-50</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Corrugated box (50 pcs)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>nos</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H6" t="n">
+        <v>120</v>
+      </c>
+      <c r="I6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ordered</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Dispatched</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Days Overdue</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Awaiting Pod</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HP/7781</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hosur Precision</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SFT-118</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PAA-4471</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pune Auto Assemblies</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HNG-310</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SM/1187</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sundaram Motors</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BRK-220</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REW/88</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rajkot Engineering Works</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BRK-221</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CP-0091</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Coimbatore Pumps</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BSH-044</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>over-sent</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HP/7790</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hosur Precision</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SFT-119</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" t="n">
+        <v>300</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HP/7795</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hosur Precision</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HNG-310</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PAA-4520</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pune Auto Assemblies</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BRK220</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>400</v>
+      </c>
+      <c r="F9" t="n">
+        <v>800</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>